--- a/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v2/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v2/Contrary(P)Body(N).xlsx
@@ -17286,13 +17286,13 @@
         <v>0.375</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.861702</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.522581</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.412698</v>
       </c>
     </row>
     <row r="3">
@@ -17345,13 +17345,13 @@
         <v>0.375</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.861702</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.522581</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.412698</v>
       </c>
     </row>
     <row r="4">
@@ -17404,13 +17404,13 @@
         <v>0.375</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.861702</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.522581</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.412698</v>
       </c>
     </row>
   </sheetData>
